--- a/data/trans_orig/IP05A06-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP05A06-Habitat-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>108865</t>
+          <t>109002</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>122979</t>
+          <t>123349</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>79,06%</t>
+          <t>79,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>120127</t>
+          <t>120927</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>136683</t>
+          <t>136214</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,36%</t>
+          <t>88,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>235110</t>
+          <t>235189</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>256645</t>
+          <t>256473</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>87,72%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13514</t>
+          <t>13527</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26880</t>
+          <t>27492</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16436</t>
+          <t>16783</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>32321</t>
+          <t>31185</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32894</t>
+          <t>32909</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53710</t>
+          <t>53464</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,25%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>18,29%</t>
         </is>
       </c>
     </row>
@@ -963,7 +963,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4554</t>
+          <t>4454</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>646</t>
+          <t>650</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5871</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1282</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7149</t>
+          <t>7100</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>137902</t>
+          <t>137928</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>157668</t>
+          <t>157534</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,66%</t>
+          <t>76,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>157885</t>
+          <t>157038</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>178023</t>
+          <t>178832</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,79%</t>
+          <t>80,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>299641</t>
+          <t>300700</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>330081</t>
+          <t>330772</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>77,14%</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45224</t>
+          <t>45528</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>65247</t>
+          <t>64676</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1316,12 +1316,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,44%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>38258</t>
+          <t>37478</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57974</t>
+          <t>57794</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>89055</t>
+          <t>88616</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>117369</t>
+          <t>117353</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1156</t>
+          <t>1121</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6376</t>
+          <t>6882</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3908</t>
+          <t>3875</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12594</t>
+          <t>12916</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>5913</t>
+          <t>6444</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16304</t>
+          <t>16415</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,83%</t>
         </is>
       </c>
     </row>
@@ -1644,12 +1644,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>104980</t>
+          <t>105089</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>122295</t>
+          <t>122502</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1659,12 +1659,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1679,12 +1679,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>104784</t>
+          <t>104559</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>122854</t>
+          <t>122357</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1694,12 +1694,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>74,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>214820</t>
+          <t>214164</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>239779</t>
+          <t>238733</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>67,12%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,6%</t>
         </is>
       </c>
     </row>
@@ -1757,12 +1757,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29574</t>
+          <t>29804</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46063</t>
+          <t>46287</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1792,12 +1792,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37195</t>
+          <t>37638</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>54602</t>
+          <t>55255</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1807,12 +1807,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71507</t>
+          <t>72762</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96288</t>
+          <t>96207</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,09%</t>
+          <t>30,06%</t>
         </is>
       </c>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1371</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8142</t>
+          <t>7976</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1905,12 +1905,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2322</t>
+          <t>2285</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>9852</t>
+          <t>9964</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1920,12 +1920,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>4829</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>15036</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -2100,12 +2100,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>110723</t>
+          <t>110168</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>134039</t>
+          <t>134587</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2115,12 +2115,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>64,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2135,12 +2135,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>118529</t>
+          <t>118933</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>141623</t>
+          <t>142584</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,06%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>68,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>235416</t>
+          <t>237496</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>268795</t>
+          <t>270058</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,94%</t>
         </is>
       </c>
     </row>
@@ -2213,12 +2213,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>62150</t>
+          <t>61915</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85026</t>
+          <t>84987</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2228,12 +2228,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,86%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58266</t>
+          <t>57850</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>80878</t>
+          <t>80826</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2263,12 +2263,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>128268</t>
+          <t>127432</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>160935</t>
+          <t>159364</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,32%</t>
         </is>
       </c>
     </row>
@@ -2326,12 +2326,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>7169</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18354</t>
+          <t>18613</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2341,12 +2341,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2361,12 +2361,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4030</t>
+          <t>3947</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>13485</t>
+          <t>13500</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2376,12 +2376,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>12928</t>
+          <t>13294</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27633</t>
+          <t>27245</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,55%</t>
         </is>
       </c>
     </row>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>481977</t>
+          <t>480324</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>522132</t>
+          <t>519340</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,87%</t>
+          <t>73,47%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2591,12 +2591,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>521058</t>
+          <t>521551</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>561508</t>
+          <t>560616</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2606,12 +2606,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>69,52%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>74,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1012527</t>
+          <t>1013972</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1071009</t>
+          <t>1072720</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>73,62%</t>
         </is>
       </c>
     </row>
@@ -2669,12 +2669,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>165609</t>
+          <t>167126</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>203476</t>
+          <t>205417</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2684,12 +2684,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2704,12 +2704,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>165371</t>
+          <t>165931</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>205451</t>
+          <t>205967</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2719,12 +2719,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>22,12%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2739,12 +2739,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>345253</t>
+          <t>344436</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>400772</t>
+          <t>400251</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2754,12 +2754,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -2782,12 +2782,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>13438</t>
+          <t>13796</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>27784</t>
+          <t>28671</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2797,12 +2797,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2817,12 +2817,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16047</t>
+          <t>16043</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31790</t>
+          <t>31349</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2837,7 +2837,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32682</t>
+          <t>33583</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53786</t>
+          <t>54020</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,71%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>113722</t>
+          <t>113335</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>125490</t>
+          <t>125160</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>126643</t>
+          <t>126358</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>138554</t>
+          <t>138190</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,9%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>244896</t>
+          <t>244065</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>261267</t>
+          <t>261081</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,34%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8065</t>
+          <t>7997</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>19455</t>
+          <t>19961</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3372,82 +3372,82 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>5,98%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>14,93%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>11186</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>6497</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>17762</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>7,66%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>4,45%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>12,17%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>23874</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>16862</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>33616</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>8,54%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>6,03%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>14,55%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>11186</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>6225</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17749</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>7,66%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>4,26%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>12,16%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>23874</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>16648</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>32674</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>8,54%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>5,95%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -3475,7 +3475,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>3247</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3490,7 +3490,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4616</t>
+          <t>4840</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3525,7 +3525,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5366</t>
+          <t>6202</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>165032</t>
+          <t>164517</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>181175</t>
+          <t>180494</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>80,07%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,9%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>177687</t>
+          <t>177691</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>195664</t>
+          <t>196116</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3755,7 +3755,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>348370</t>
+          <t>347880</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>371538</t>
+          <t>373097</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>86,67%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>22972</t>
+          <t>23294</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>38942</t>
+          <t>39141</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>25101</t>
+          <t>24244</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>42097</t>
+          <t>41673</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>51612</t>
+          <t>51956</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>73921</t>
+          <t>75119</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,45%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>577</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>5522</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1974</t>
+          <t>1925</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9260</t>
+          <t>9359</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3713</t>
+          <t>3505</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>11931</t>
+          <t>12604</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,93%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>95474</t>
+          <t>95119</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>112495</t>
+          <t>113797</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>73,2%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>107314</t>
+          <t>107497</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>126196</t>
+          <t>127277</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>208195</t>
+          <t>207155</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>234183</t>
+          <t>234419</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>64,63%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,77%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>35962</t>
+          <t>35431</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52661</t>
+          <t>53619</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,87%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>32141</t>
+          <t>30976</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>50009</t>
+          <t>49700</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72086</t>
+          <t>71934</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96041</t>
+          <t>97002</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,38%</t>
+          <t>22,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,11%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3902</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>12606</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4794</t>
+          <t>5104</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15022</t>
+          <t>14766</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10539</t>
+          <t>10867</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23135</t>
+          <t>24230</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,52%</t>
         </is>
       </c>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>118761</t>
+          <t>117815</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>141762</t>
+          <t>141353</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,77%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4647,12 +4647,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>116248</t>
+          <t>116639</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>139134</t>
+          <t>137661</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>57,11%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>67,4%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>242416</t>
+          <t>242700</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>273039</t>
+          <t>273652</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>66,78%</t>
         </is>
       </c>
     </row>
@@ -4725,12 +4725,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>50708</t>
+          <t>50556</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72191</t>
+          <t>72594</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4740,12 +4740,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,6%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>35,32%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4760,12 +4760,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>52299</t>
+          <t>54178</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74454</t>
+          <t>75385</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>36,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>110532</t>
+          <t>108856</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>140584</t>
+          <t>140265</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,23%</t>
         </is>
       </c>
     </row>
@@ -4838,12 +4838,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>8584</t>
+          <t>8128</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21241</t>
+          <t>21440</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4853,12 +4853,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4873,12 +4873,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>8067</t>
+          <t>7813</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19141</t>
+          <t>18934</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19703</t>
+          <t>18793</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>35639</t>
+          <t>35804</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,74%</t>
         </is>
       </c>
     </row>
@@ -5068,12 +5068,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>509154</t>
+          <t>510973</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>544977</t>
+          <t>547347</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5083,12 +5083,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>78,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>547125</t>
+          <t>545335</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>583631</t>
+          <t>583776</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1067061</t>
+          <t>1067112</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1119577</t>
+          <t>1120447</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,7%</t>
         </is>
       </c>
     </row>
@@ -5181,12 +5181,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>131602</t>
+          <t>130626</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>166175</t>
+          <t>164966</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5196,12 +5196,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,54%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5216,12 +5216,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>130923</t>
+          <t>130996</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>165223</t>
+          <t>166622</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>17,67%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,29%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>273079</t>
+          <t>272046</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>322383</t>
+          <t>322596</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>16639</t>
+          <t>16855</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>32281</t>
+          <t>32600</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5309,12 +5309,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5329,12 +5329,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20188</t>
+          <t>19343</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>36990</t>
+          <t>37074</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5344,12 +5344,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40911</t>
+          <t>41939</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>64542</t>
+          <t>65249</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,12 +5379,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -5756,12 +5756,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>108649</t>
+          <t>108163</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>115675</t>
+          <t>115646</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5771,12 +5771,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5791,12 +5791,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>125058</t>
+          <t>123676</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>136070</t>
+          <t>135961</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>89,06%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5826,12 +5826,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>237115</t>
+          <t>236295</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>250446</t>
+          <t>249977</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,19%</t>
+          <t>97,01%</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5869,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1605</t>
+          <t>1634</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8631</t>
+          <t>9117</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5884,12 +5884,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5904,12 +5904,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3040</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12433</t>
+          <t>13606</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5939,12 +5939,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6132</t>
+          <t>6231</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18092</t>
+          <t>18462</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>7410</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6057,7 +6057,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8230</t>
+          <t>9733</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,78%</t>
         </is>
       </c>
     </row>
@@ -6212,12 +6212,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>159656</t>
+          <t>158908</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>175298</t>
+          <t>175101</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6227,12 +6227,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6247,12 +6247,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>221046</t>
+          <t>220760</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>238521</t>
+          <t>238743</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,94%</t>
+          <t>86,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6282,12 +6282,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>386171</t>
+          <t>384586</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>409957</t>
+          <t>409455</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,83%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>92,06%</t>
         </is>
       </c>
     </row>
@@ -6325,12 +6325,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>10229</t>
+          <t>10724</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24278</t>
+          <t>25258</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6340,12 +6340,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6360,12 +6360,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>9022</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23969</t>
+          <t>24850</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6375,12 +6375,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6395,12 +6395,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>22548</t>
+          <t>22551</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>43205</t>
+          <t>43250</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -6438,12 +6438,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>2869</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11220</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6453,12 +6453,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>4017</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15880</t>
+          <t>15264</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6488,12 +6488,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6508,12 +6508,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8951</t>
+          <t>8473</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22525</t>
+          <t>22162</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>75963</t>
+          <t>74914</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>155151</t>
+          <t>154995</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>39,9%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6703,12 +6703,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>131445</t>
+          <t>133029</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>155729</t>
+          <t>155177</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6718,12 +6718,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>71,3%</t>
+          <t>72,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6738,12 +6738,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>215457</t>
+          <t>212426</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>303523</t>
+          <t>300408</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6753,12 +6753,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>56,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,16%</t>
         </is>
       </c>
     </row>
@@ -6781,12 +6781,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>16604</t>
+          <t>16589</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39877</t>
+          <t>40515</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6816,12 +6816,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21292</t>
+          <t>21710</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44379</t>
+          <t>42929</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6851,12 +6851,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42771</t>
+          <t>42248</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76213</t>
+          <t>75500</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6866,12 +6866,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,34%</t>
+          <t>20,15%</t>
         </is>
       </c>
     </row>
@@ -6894,12 +6894,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6133</t>
+          <t>5574</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>99069</t>
+          <t>100787</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6909,12 +6909,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6929,12 +6929,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>4413</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15110</t>
+          <t>15216</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6944,12 +6944,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13516</t>
+          <t>13613</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>126528</t>
+          <t>118668</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6979,12 +6979,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>33,76%</t>
+          <t>31,66%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>110521</t>
+          <t>109785</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>130276</t>
+          <t>129891</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,36%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>114169</t>
+          <t>115262</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>137564</t>
+          <t>138373</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>231840</t>
+          <t>232861</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>262127</t>
+          <t>261681</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,45%</t>
         </is>
       </c>
     </row>
@@ -7237,12 +7237,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22930</t>
+          <t>23141</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>41413</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7252,12 +7252,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,89%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7272,12 +7272,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24141</t>
+          <t>23966</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43460</t>
+          <t>43296</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7287,12 +7287,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7307,12 +7307,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51600</t>
+          <t>50788</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>77983</t>
+          <t>75792</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7322,12 +7322,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -7350,12 +7350,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9591</t>
+          <t>9435</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>22199</t>
+          <t>21915</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7365,12 +7365,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,33%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7385,12 +7385,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13861</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>28721</t>
+          <t>29151</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7400,12 +7400,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,17%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7420,12 +7420,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>27850</t>
+          <t>26051</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>46303</t>
+          <t>45810</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7435,12 +7435,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>13,21%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>457389</t>
+          <t>454155</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>559959</t>
+          <t>560814</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7595,12 +7595,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>84,24%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>614974</t>
+          <t>614706</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>654875</t>
+          <t>656060</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1078915</t>
+          <t>1095391</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1199255</t>
+          <t>1200342</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,29%</t>
         </is>
       </c>
     </row>
@@ -7693,12 +7693,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>64543</t>
+          <t>64263</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>95937</t>
+          <t>96166</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7708,12 +7708,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>14,43%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7728,12 +7728,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>69007</t>
+          <t>67849</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>104579</t>
+          <t>103397</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7743,12 +7743,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>141307</t>
+          <t>141994</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>188818</t>
+          <t>191392</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,44%</t>
         </is>
       </c>
     </row>
@@ -7806,12 +7806,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26106</t>
+          <t>25639</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>135692</t>
+          <t>139205</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7821,12 +7821,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7841,12 +7841,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28760</t>
+          <t>28883</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>50755</t>
+          <t>49983</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7856,12 +7856,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7876,12 +7876,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62840</t>
+          <t>62505</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>192037</t>
+          <t>182731</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7891,12 +7891,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>12,83%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP05A06-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP05A06-Habitat-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>129834</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>121323</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>137289</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>83,94%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>78,43%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>88,75%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>116901</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>109002</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>123349</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>109716</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>123731</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>84,89%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>79,16%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>89,58%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>129834</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>120927</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>136214</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>83,94%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>235189</t>
+          <t>235309</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>256473</t>
+          <t>256178</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,62%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>22867</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15463</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>31290</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>14,78%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>20,23%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>19514</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>13527</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>27492</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>13063</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>26922</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>14,17%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9,82%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>19,96%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>22867</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>16783</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>31185</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>14,78%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32909</t>
+          <t>32919</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>53464</t>
+          <t>52992</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,12%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1982</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>651</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5298</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>3,43%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1290</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>4454</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>3989</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,94%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>3,23%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1982</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5348</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>7100</t>
+          <t>7892</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -1061,57 +1061,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>154684</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>137705</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>137705</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>137705</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>154684</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1178,72 +1178,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>168073</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>156740</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>177875</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>75,33%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>70,25%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>79,72%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>147625</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>137928</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>157534</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>136654</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>156898</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>71,77%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>67,06%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>76,59%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>168073</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>157038</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>178832</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>75,33%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>70,38%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>80,15%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>300700</t>
+          <t>300448</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>330772</t>
+          <t>329816</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,13%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,14%</t>
+          <t>76,92%</t>
         </is>
       </c>
     </row>
@@ -1291,72 +1291,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47713</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>38233</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>57359</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>21,39%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>17,14%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>25,71%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>86</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>54935</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>45528</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>64676</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>45878</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>65817</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>26,71%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>22,14%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>31,44%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>47713</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>37478</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>57794</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>21,39%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1371,12 +1371,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>88616</t>
+          <t>89850</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>117353</t>
+          <t>117283</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1386,12 +1386,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>27,35%</t>
         </is>
       </c>
     </row>
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7328</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3982</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>12331</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,28%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,78%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3123</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1121</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>6882</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1152</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>7184</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,52%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,35%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>7328</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>3875</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>12916</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6444</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16415</t>
+          <t>16402</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1517,57 +1517,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>223115</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>223115</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>223115</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>318</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>205683</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>205683</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>205683</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>323</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>223115</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>223115</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>223115</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1634,72 +1634,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>113613</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>103604</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>122661</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>69,0%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>62,92%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>74,5%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>176</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>113659</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>105089</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>122502</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>103819</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>121398</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>73,15%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>67,64%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>78,84%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>113613</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>104559</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>122357</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>69,0%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>63,5%</t>
+          <t>66,82%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>78,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1714,12 +1714,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>214164</t>
+          <t>214834</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>238733</t>
+          <t>239269</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1729,12 +1729,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,76%</t>
         </is>
       </c>
     </row>
@@ -1747,72 +1747,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>45991</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>37889</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>56202</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>27,93%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>23,01%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>34,13%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>37773</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>29804</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>46287</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>30169</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>46976</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>24,31%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>19,18%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>29,79%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>45991</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>37638</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>55255</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>27,93%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1827,12 +1827,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>72762</t>
+          <t>71211</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>96207</t>
+          <t>96523</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1842,12 +1842,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,16%</t>
         </is>
       </c>
     </row>
@@ -1860,72 +1860,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5052</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2299</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9535</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5,79%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>3944</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1410</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>7976</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>1392</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>8084</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>2,54%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>5052</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2285</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>9964</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>4829</t>
+          <t>5001</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15036</t>
+          <t>14128</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1955,12 +1955,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,41%</t>
         </is>
       </c>
     </row>
@@ -1973,57 +1973,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>164656</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>164656</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>164656</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>242</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>155376</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>155376</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>164656</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>164656</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>164656</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2090,72 +2090,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>130426</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>118540</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>142840</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>62,79%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>57,06%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>68,76%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>160</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>122751</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>110168</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>134587</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>110817</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>134503</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>58,99%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>52,94%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>64,67%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>130426</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>118933</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>142584</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>62,79%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,64%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2170,12 +2170,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>237496</t>
+          <t>236923</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>270058</t>
+          <t>270139</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>56,98%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,96%</t>
         </is>
       </c>
     </row>
@@ -2203,72 +2203,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>69368</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>57946</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>81286</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>33,39%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>27,89%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>39,13%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>73574</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>61915</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>84987</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>61868</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>85370</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>35,35%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>29,75%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>40,84%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>69368</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>57850</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>80826</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>33,39%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>29,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>41,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>127432</t>
+          <t>126231</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>159364</t>
+          <t>158709</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2298,12 +2298,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>30,65%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,17%</t>
         </is>
       </c>
     </row>
@@ -2316,72 +2316,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7935</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>4192</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>13681</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,02%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>6,59%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>11777</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>7169</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>18613</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>7054</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>18573</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>5,66%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,45%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>8,94%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>7935</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>3947</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>13500</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2396,12 +2396,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13294</t>
+          <t>13689</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>27245</t>
+          <t>28872</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -2429,57 +2429,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>207729</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>207729</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>207729</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>272</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>208102</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>208102</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>208102</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>207729</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>207729</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>207729</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2546,72 +2546,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>769</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>541946</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>520440</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>561708</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>72,24%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>69,37%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>74,88%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>722</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>500936</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>480324</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>519340</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>480038</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>519877</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>70,87%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>67,95%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>73,47%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>769</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>541946</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>521551</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>560616</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>72,24%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,73%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2626,12 +2626,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1013972</t>
+          <t>1015281</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1072720</t>
+          <t>1072207</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2641,12 +2641,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,59%</t>
         </is>
       </c>
     </row>
@@ -2664,102 +2664,102 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>185940</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>166440</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>206480</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>24,79%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>22,19%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>27,52%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
           <t>185795</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>167126</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>205417</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>167764</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>206091</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>26,28%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>23,73%</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>29,16%</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr">
+        <is>
+          <t>536</t>
+        </is>
+      </c>
+      <c r="R21" s="2" t="inlineStr">
+        <is>
+          <t>371735</t>
+        </is>
+      </c>
+      <c r="S21" s="2" t="inlineStr">
+        <is>
+          <t>344406</t>
+        </is>
+      </c>
+      <c r="T21" s="2" t="inlineStr">
+        <is>
+          <t>398593</t>
+        </is>
+      </c>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>25,51%</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>23,64%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>29,06%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>185940</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>165931</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>205967</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>24,79%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>22,12%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>27,46%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>536</t>
-        </is>
-      </c>
-      <c r="R21" s="2" t="inlineStr">
-        <is>
-          <t>371735</t>
-        </is>
-      </c>
-      <c r="S21" s="2" t="inlineStr">
-        <is>
-          <t>344436</t>
-        </is>
-      </c>
-      <c r="T21" s="2" t="inlineStr">
-        <is>
-          <t>400251</t>
-        </is>
-      </c>
-      <c r="U21" s="2" t="inlineStr">
-        <is>
-          <t>25,51%</t>
-        </is>
-      </c>
-      <c r="V21" s="2" t="inlineStr">
-        <is>
-          <t>23,64%</t>
-        </is>
-      </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,36%</t>
         </is>
       </c>
     </row>
@@ -2772,72 +2772,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>22298</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>15430</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>30943</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2,97%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>20134</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>13796</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>28671</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>13684</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>28845</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>2,85%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>4,06%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>22298</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>16043</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>31349</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2852,12 +2852,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>33583</t>
+          <t>33324</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>54020</t>
+          <t>54151</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2867,12 +2867,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,72%</t>
         </is>
       </c>
     </row>
@@ -2885,57 +2885,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1070</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>750184</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>750184</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>750184</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1019</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>706866</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>706866</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>706866</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1070</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>750184</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>750184</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>750184</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -3055,7 +3055,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3066,7 +3066,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>133386</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>126841</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>138531</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>91,36%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>86,88%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>94,89%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>120433</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>113335</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>125160</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>113435</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>125413</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>90,07%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>84,76%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>93,61%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>133386</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>126358</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>138190</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>91,36%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>86,55%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,66%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>244065</t>
+          <t>244342</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>261081</t>
+          <t>261004</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>87,26%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>93,32%</t>
         </is>
       </c>
     </row>
@@ -3347,72 +3347,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11186</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6481</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17713</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>7,66%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>12,13%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>12688</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>7997</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>19961</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>8011</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>19748</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>9,49%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>5,98%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>14,93%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>11186</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>6497</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17762</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>7,66%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>16862</t>
+          <t>17077</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>33616</t>
+          <t>33505</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,98%</t>
         </is>
       </c>
     </row>
@@ -3460,72 +3460,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1422</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>4958</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>586</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3224</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>2633</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,44%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1422</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>4840</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>582</t>
+          <t>581</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6202</t>
+          <t>5545</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -3573,57 +3573,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>145993</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>145993</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>145993</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>187</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>133707</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>133707</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>145993</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>145993</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>145993</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3690,72 +3690,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>187415</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>177288</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>195867</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>83,53%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>79,02%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>87,3%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>278</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>173195</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>164517</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>180494</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>164808</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>180531</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>84,03%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>79,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>87,57%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>276</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>187415</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>177691</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>196116</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>83,53%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,59%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>347880</t>
+          <t>347744</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>373097</t>
+          <t>372916</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,67%</t>
+          <t>86,63%</t>
         </is>
       </c>
     </row>
@@ -3803,72 +3803,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>32377</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>24254</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>41538</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>14,43%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>10,81%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>18,51%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>30597</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>23294</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>39141</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>23469</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>39169</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>14,84%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>11,3%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>18,99%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>32377</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>24244</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>41673</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>14,43%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>51956</t>
+          <t>51150</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>75119</t>
+          <t>75128</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3898,7 +3898,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -3916,72 +3916,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4567</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1929</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>9110</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2,04%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,06%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>2318</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>577</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>5522</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5463</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>1,12%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,68%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>4567</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1925</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>9359</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3505</t>
+          <t>3642</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>12604</t>
+          <t>12141</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -4034,52 +4034,52 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>224359</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
           <t>206110</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>206110</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>206110</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>224359</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4151,67 +4151,67 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>117661</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>107677</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>127205</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>70,59%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>64,6%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>76,32%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
           <t>104258</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>95119</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>113797</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>95219</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>113485</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>67,07%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>61,19%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>73,2%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>117661</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>107497</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>127277</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>70,59%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>61,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>73,0%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>207155</t>
+          <t>208967</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>234419</t>
+          <t>235142</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>64,31%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>73,0%</t>
         </is>
       </c>
     </row>
@@ -4259,74 +4259,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>40062</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>31677</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>49500</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>24,04%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>19,01%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>29,7%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>43884</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>35431</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>53619</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>35754</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>53623</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>28,23%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>22,79%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>23,0%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>34,49%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>40062</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>30976</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>49700</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>24,04%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>18,58%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>29,82%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>128</t>
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71934</t>
+          <t>71160</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>97002</t>
+          <t>96480</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,33%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,95%</t>
         </is>
       </c>
     </row>
@@ -4377,67 +4377,67 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>8949</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4631</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15080</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5,37%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2,78%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9,05%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>7316</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>4077</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>12606</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>3704</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>12136</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>4,71%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,62%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>8,11%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>8949</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>5104</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>14766</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>5,37%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10867</t>
+          <t>11277</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24230</t>
+          <t>23993</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -4485,57 +4485,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166673</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>155457</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>155457</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>155457</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>166673</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4602,72 +4602,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>127183</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>115085</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>138318</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>62,27%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>56,35%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>67,72%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>131072</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>117815</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>141353</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>120102</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>142860</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>63,77%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>57,32%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>68,77%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>127183</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>116639</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>137661</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>62,27%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,11%</t>
+          <t>58,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>67,4%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4682,12 +4682,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>242700</t>
+          <t>242538</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>273652</t>
+          <t>274663</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>59,22%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,78%</t>
+          <t>67,02%</t>
         </is>
       </c>
     </row>
@@ -4715,72 +4715,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>64152</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>53890</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>75800</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>31,41%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>26,38%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>37,11%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>60706</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>50556</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>72594</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>51023</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>72906</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>29,53%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>24,6%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>35,32%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>64152</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>54178</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>75385</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>31,41%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>26,53%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>35,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4795,12 +4795,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>108856</t>
+          <t>109574</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>140265</t>
+          <t>140112</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,19%</t>
         </is>
       </c>
     </row>
@@ -4833,67 +4833,67 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>12916</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>8463</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>19199</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>6,32%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4,14%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>9,4%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
           <t>13769</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>8128</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>21440</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>8839</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>20737</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>6,7%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>10,43%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>12916</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>7813</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>18934</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>6,32%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4908,12 +4908,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>18793</t>
+          <t>19087</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>35804</t>
+          <t>34784</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -4941,57 +4941,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>204251</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>204251</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>204251</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>278</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>205547</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>205547</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>205547</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>204251</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>204251</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>204251</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5058,72 +5058,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>805</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>565645</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>547488</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>586956</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>76,31%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>73,86%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>79,18%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>798</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>528958</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>510973</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>547347</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>509882</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>546778</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>75,48%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>72,91%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>78,1%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>805</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>565645</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>545335</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>583776</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>76,31%</t>
-        </is>
-      </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>72,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5138,12 +5138,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1067112</t>
+          <t>1067524</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1120447</t>
+          <t>1121108</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,74%</t>
         </is>
       </c>
     </row>
@@ -5171,72 +5171,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>147777</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>128331</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>165703</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>19,94%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>17,31%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>22,35%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>147875</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>130626</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>164966</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>130359</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>166493</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>21,1%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>18,64%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>23,54%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>215</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>147777</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>130996</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>166622</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>19,94%</t>
-        </is>
-      </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5251,12 +5251,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>272046</t>
+          <t>271058</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>322596</t>
+          <t>322005</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,33%</t>
         </is>
       </c>
     </row>
@@ -5284,72 +5284,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>27854</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>20078</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>37709</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>3,76%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5,09%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>23989</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>16855</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>32600</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>17168</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>32524</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>3,42%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>4,65%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>27854</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>19343</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>37074</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>3,76%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5364,12 +5364,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41939</t>
+          <t>41356</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>65249</t>
+          <t>65251</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5379,7 +5379,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -5397,57 +5397,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1060</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>741276</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>741276</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>741276</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>1055</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>700822</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>700822</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="M23" s="2" t="inlineStr">
         <is>
           <t>700822</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>1060</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>741276</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>741276</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>741276</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5567,7 +5567,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -5578,7 +5578,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -5746,72 +5746,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>118117</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>109751</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>121854</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>93,81%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>87,17%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>96,78%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>190</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>113055</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>108163</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>115646</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>96,4%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>92,23%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>98,61%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>132064</t>
+          <t>116531</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>123676</t>
+          <t>112075</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>135961</t>
+          <t>119069</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5821,32 +5821,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>245120</t>
+          <t>234648</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>236295</t>
+          <t>227253</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>249977</t>
+          <t>240277</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -5859,72 +5859,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>6022</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2873</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>12240</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>9,72%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>4225</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1634</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9117</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>3,6%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,39%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>7,77%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>4540</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3023</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13606</t>
+          <t>8996</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5934,32 +5934,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>10732</t>
+          <t>10562</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6231</t>
+          <t>5962</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18462</t>
+          <t>17727</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -5972,107 +5972,107 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1767</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9510</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,18%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7,55%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="Q6" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>1841</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>1767</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>7410</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,31%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>7869</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,72%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>5,28%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1841</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>9733</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -6085,57 +6085,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>125906</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>196</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>117280</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>140412</t>
+          <t>121071</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>257693</t>
+          <t>246977</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6202,107 +6202,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>215082</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>205334</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>222178</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>90,92%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>86,8%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>93,92%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>249</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>168227</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>158908</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>175101</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>88,3%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83,41%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>162422</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>153365</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>169225</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>88,08%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>83,16%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>91,76%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>560</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>377504</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>364598</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>386922</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>89,67%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>86,61%</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
         <is>
           <t>91,91%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>311</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>230815</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>220760</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>238743</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>90,78%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>86,83%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>93,9%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>560</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>399043</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>384586</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>409455</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>89,72%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>86,47%</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>92,06%</t>
         </is>
       </c>
     </row>
@@ -6315,72 +6315,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>14049</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>8381</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>21993</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>3,54%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>9,3%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>16324</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>10724</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>25258</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>8,57%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>13,26%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15165</t>
+          <t>15963</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8670</t>
+          <t>10096</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24850</t>
+          <t>23525</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6390,32 +6390,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>31489</t>
+          <t>30012</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>22551</t>
+          <t>21303</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>43250</t>
+          <t>40424</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,6%</t>
         </is>
       </c>
     </row>
@@ -6428,72 +6428,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>7430</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3559</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>14496</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>3,14%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,13%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>5961</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2869</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>10426</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,51%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>8274</t>
+          <t>6028</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4017</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15264</t>
+          <t>11208</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6503,17 +6503,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>14236</t>
+          <t>13458</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22162</t>
+          <t>21392</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6523,12 +6523,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,08%</t>
         </is>
       </c>
     </row>
@@ -6541,57 +6541,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>236561</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>236561</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>236561</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>280</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>190512</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>341</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>254254</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>254254</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>254254</t>
+          <t>184413</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6616,17 +6616,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>444767</t>
+          <t>420973</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>444767</t>
+          <t>420973</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>444767</t>
+          <t>420973</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6658,72 +6658,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>133924</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>123923</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>142783</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>80,01%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>74,04%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>85,3%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>178</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>129438</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>74914</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>154995</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>67,98%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>39,35%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>81,4%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>145405</t>
+          <t>123538</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>133029</t>
+          <t>112943</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>155177</t>
+          <t>131741</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>78,87%</t>
+          <t>78,66%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>83,89%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6733,32 +6733,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>274843</t>
+          <t>257461</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>212426</t>
+          <t>244140</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>300408</t>
+          <t>270188</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>80,16%</t>
+          <t>83,28%</t>
         </is>
       </c>
     </row>
@@ -6771,72 +6771,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25062</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>16997</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>33555</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>14,97%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>10,15%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>20,05%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>27777</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>16589</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>40515</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>14,59%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,71%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>21,28%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30553</t>
+          <t>24489</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21710</t>
+          <t>17512</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>42929</t>
+          <t>32864</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6846,32 +6846,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>58329</t>
+          <t>49551</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>42248</t>
+          <t>38809</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75500</t>
+          <t>61359</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,56%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,27%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>18,91%</t>
         </is>
       </c>
     </row>
@@ -6884,72 +6884,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>8398</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4257</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>17213</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5,02%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>10,28%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>33187</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>5574</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>100787</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>17,43%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>52,93%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>8405</t>
+          <t>9023</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4413</t>
+          <t>4083</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15216</t>
+          <t>19626</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6959,32 +6959,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>41592</t>
+          <t>17421</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13613</t>
+          <t>10245</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>118668</t>
+          <t>28555</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -6997,57 +6997,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>167384</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>167384</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>167384</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>227</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>190401</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>224</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>184363</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>184363</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>184363</t>
+          <t>157050</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7072,17 +7072,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>374764</t>
+          <t>324433</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>374764</t>
+          <t>324433</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>374764</t>
+          <t>324433</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7114,72 +7114,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>116978</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>106548</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>126678</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>69,46%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>63,26%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>75,22%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>173</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>120773</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>109785</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>129891</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>72,52%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>65,92%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>77,99%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>126710</t>
+          <t>119862</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115262</t>
+          <t>110296</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>138373</t>
+          <t>129221</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>63,93%</t>
+          <t>66,19%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>247483</t>
+          <t>236840</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>232861</t>
+          <t>222376</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>261681</t>
+          <t>250555</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>71,35%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>74,78%</t>
         </is>
       </c>
     </row>
@@ -7227,72 +7227,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>31444</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>23545</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>40510</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>18,67%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>13,98%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>24,05%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>30546</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>23141</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>41413</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>18,34%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>13,89%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>24,87%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>33078</t>
+          <t>31511</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23966</t>
+          <t>22271</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>43296</t>
+          <t>39902</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7302,32 +7302,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>63624</t>
+          <t>62955</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>50788</t>
+          <t>51897</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>75792</t>
+          <t>77016</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>22,99%</t>
         </is>
       </c>
     </row>
@@ -7340,72 +7340,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>19997</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>13498</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>27933</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>11,87%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>8,01%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>16,59%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>22</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>15226</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>9435</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>21915</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>9,14%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,67%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>13,16%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>20507</t>
+          <t>15275</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13938</t>
+          <t>10182</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>29151</t>
+          <t>22983</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7415,32 +7415,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>35733</t>
+          <t>35271</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>26051</t>
+          <t>26631</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>45810</t>
+          <t>45483</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,57%</t>
         </is>
       </c>
     </row>
@@ -7453,57 +7453,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>168419</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>166545</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>166545</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>166545</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>166648</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>166648</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>180295</t>
+          <t>166648</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7528,17 +7528,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>346840</t>
+          <t>335067</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>346840</t>
+          <t>335067</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>346840</t>
+          <t>335067</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7570,72 +7570,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>584101</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>565795</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>601647</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>83,65%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>81,03%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>86,16%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>790</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>531493</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>454155</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>560814</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>79,96%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>68,32%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>84,37%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>634995</t>
+          <t>522354</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>614706</t>
+          <t>506155</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>656060</t>
+          <t>537882</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1166488</t>
+          <t>1106454</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1095391</t>
+          <t>1082258</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1200342</t>
+          <t>1129283</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>81,91%</t>
+          <t>83,35%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>81,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>85,07%</t>
         </is>
       </c>
     </row>
@@ -7683,72 +7683,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>76577</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>62287</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>93238</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>10,97%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>8,92%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>13,35%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>110</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>78871</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>64263</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>96166</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>11,86%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>9,67%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>14,47%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>104</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>85303</t>
+          <t>76502</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>67849</t>
+          <t>63174</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>103397</t>
+          <t>90246</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>10,04%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>164174</t>
+          <t>153080</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>141994</t>
+          <t>133996</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>191392</t>
+          <t>177105</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7778,12 +7778,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,34%</t>
         </is>
       </c>
     </row>
@@ -7796,72 +7796,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>37591</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>27844</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>49619</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>3,99%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>7,11%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>54374</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>25639</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>139205</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>8,18%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>3,86%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>20,94%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>39027</t>
+          <t>30326</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>28883</t>
+          <t>21967</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>49983</t>
+          <t>41804</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7871,32 +7871,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>93401</t>
+          <t>67917</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>62505</t>
+          <t>53384</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>182731</t>
+          <t>82512</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -7909,57 +7909,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>973</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>698270</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>698270</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>698270</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>973</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>759325</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>759325</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>759325</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7984,17 +7984,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1424063</t>
+          <t>1327451</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1424063</t>
+          <t>1327451</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1424063</t>
+          <t>1327451</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
